--- a/public/templates/RadiographyMobile_Test_Template.xlsx
+++ b/public/templates/RadiographyMobile_Test_Template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="177">
   <si>
     <t>Field Name</t>
   </si>
